--- a/sub_pro_12_fifa_tm_analysis/datasets/concacaf_squad_value_mar_2026.xlsx
+++ b/sub_pro_12_fifa_tm_analysis/datasets/concacaf_squad_value_mar_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\sports_data_sci\sub_pro_12_fifa_tm_analysis\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3856C46-11DF-4AC8-9D46-8238BEED43B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C4CCF5-EA1C-4006-B877-A0814B0379B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{76156EE3-C0DD-4115-B795-61CF6E833711}"/>
+    <workbookView xWindow="340" yWindow="0" windowWidth="9050" windowHeight="10070" xr2:uid="{76156EE3-C0DD-4115-B795-61CF6E833711}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
-  <si>
-    <t>Countries</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>Type</t>
   </si>
@@ -181,6 +178,93 @@
   </si>
   <si>
     <t>€9k</t>
+  </si>
+  <si>
+    <t>Most valuable player</t>
+  </si>
+  <si>
+    <t>Value of Player</t>
+  </si>
+  <si>
+    <t>€400k</t>
+  </si>
+  <si>
+    <t>Luther James-Wildin</t>
+  </si>
+  <si>
+    <t>Niall Reid-Stephen</t>
+  </si>
+  <si>
+    <t>Krisean López</t>
+  </si>
+  <si>
+    <t>€125k</t>
+  </si>
+  <si>
+    <t>Jorge Aguirre</t>
+  </si>
+  <si>
+    <t>€600k</t>
+  </si>
+  <si>
+    <t>Pablo Rosario</t>
+  </si>
+  <si>
+    <t>€8.00m</t>
+  </si>
+  <si>
+    <t>Regan Charles-Cook</t>
+  </si>
+  <si>
+    <t>Osaze De Rosario</t>
+  </si>
+  <si>
+    <t>€800k</t>
+  </si>
+  <si>
+    <t>Wilson Isidor</t>
+  </si>
+  <si>
+    <t>€18.00m</t>
+  </si>
+  <si>
+    <t>Leon Bailey</t>
+  </si>
+  <si>
+    <t>€16.00m</t>
+  </si>
+  <si>
+    <t>Arkell Jude-Boyd</t>
+  </si>
+  <si>
+    <t>€150k</t>
+  </si>
+  <si>
+    <t>Tyrese Shade</t>
+  </si>
+  <si>
+    <t>€225k</t>
+  </si>
+  <si>
+    <t>Oalex Anderson</t>
+  </si>
+  <si>
+    <t>Joël Piroe</t>
+  </si>
+  <si>
+    <t>€13.00m</t>
+  </si>
+  <si>
+    <t>Levi García</t>
+  </si>
+  <si>
+    <t>€7.50m</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Ranking</t>
   </si>
 </sst>
 </file>
@@ -545,407 +629,562 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6A17EE-8022-4794-AEA0-44B800B20CFF}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>165</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F2" s="2">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>206</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>178</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>181</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2">
+        <v>26.8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>166</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2">
+        <v>23.8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>183</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2">
+        <v>25.7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>142</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2">
+        <v>23</v>
+      </c>
+      <c r="F8" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>164</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>151</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2">
+        <v>26</v>
+      </c>
+      <c r="F10" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2">
         <v>25</v>
       </c>
-      <c r="D3">
-        <v>21</v>
-      </c>
-      <c r="E3">
-        <v>21.5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F11" s="2">
+        <v>27.6</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>70</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>167</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2">
+        <v>23</v>
+      </c>
+      <c r="F13" s="2">
+        <v>26.6</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4">
+      <c r="H13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>154</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="2">
         <v>23</v>
       </c>
-      <c r="E4">
-        <v>24.6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="F14" s="2">
+        <v>27.4</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2">
+        <v>32</v>
+      </c>
+      <c r="F15" s="2">
+        <v>25</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>123</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>26.8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>23.8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>25.7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>24.6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>25.3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10">
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2">
         <v>26</v>
       </c>
-      <c r="E10">
-        <v>26.1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11">
-        <v>25</v>
-      </c>
-      <c r="E11">
-        <v>27.6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12">
+      <c r="F16" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="2">
+        <v>22</v>
+      </c>
+      <c r="F17" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E12">
-        <v>27.5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
-        <v>23</v>
-      </c>
-      <c r="E13">
-        <v>26.6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14">
-        <v>23</v>
-      </c>
-      <c r="E14">
-        <v>27.4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15">
-        <v>32</v>
-      </c>
-      <c r="E15">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16">
-        <v>26</v>
-      </c>
-      <c r="E16">
-        <v>28.9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17">
-        <v>22</v>
-      </c>
-      <c r="E17">
-        <v>24.9</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G17" t="s">
-        <v>29</v>
+      <c r="I17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/sub_pro_12_fifa_tm_analysis/datasets/concacaf_squad_value_mar_2026.xlsx
+++ b/sub_pro_12_fifa_tm_analysis/datasets/concacaf_squad_value_mar_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\sports_data_sci\sub_pro_12_fifa_tm_analysis\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C4CCF5-EA1C-4006-B877-A0814B0379B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5FD7C8-174E-4984-A56F-5685699D4F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="0" windowWidth="9050" windowHeight="10070" xr2:uid="{76156EE3-C0DD-4115-B795-61CF6E833711}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{76156EE3-C0DD-4115-B795-61CF6E833711}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>Type</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Ranking</t>
+  </si>
+  <si>
+    <t>Players playing abroad (%)</t>
   </si>
 </sst>
 </file>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6A17EE-8022-4794-AEA0-44B800B20CFF}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
@@ -638,12 +641,13 @@
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
@@ -674,8 +678,11 @@
       <c r="J1" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>165</v>
       </c>
@@ -706,8 +713,11 @@
       <c r="J2" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K2">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>206</v>
       </c>
@@ -738,8 +748,11 @@
       <c r="J3" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K3">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>178</v>
       </c>
@@ -770,8 +783,11 @@
       <c r="J4" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K4">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>181</v>
       </c>
@@ -802,8 +818,11 @@
       <c r="J5" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>166</v>
       </c>
@@ -834,8 +853,11 @@
       <c r="J6" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>183</v>
       </c>
@@ -866,8 +888,11 @@
       <c r="J7" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>142</v>
       </c>
@@ -898,8 +923,11 @@
       <c r="J8" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>164</v>
       </c>
@@ -930,8 +958,11 @@
       <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K9">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>151</v>
       </c>
@@ -962,8 +993,11 @@
       <c r="J10" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K10">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>83</v>
       </c>
@@ -994,8 +1028,11 @@
       <c r="J11" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>70</v>
       </c>
@@ -1026,8 +1063,11 @@
       <c r="J12" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K12">
+        <v>92.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>167</v>
       </c>
@@ -1058,8 +1098,11 @@
       <c r="J13" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K13">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>154</v>
       </c>
@@ -1090,8 +1133,11 @@
       <c r="J14" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>171</v>
       </c>
@@ -1122,8 +1168,11 @@
       <c r="J15" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K15">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>123</v>
       </c>
@@ -1154,8 +1203,11 @@
       <c r="J16" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>97</v>
       </c>
@@ -1185,6 +1237,9 @@
       </c>
       <c r="J17" s="2" t="s">
         <v>77</v>
+      </c>
+      <c r="K17">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
